--- a/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F76A7F97-6DED-43B3-B960-A38F6C38918F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9782ED8-0FDD-4D11-918B-E6C9C7A074FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -783,13 +783,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S03aH03,S01aH06,S02aH03,S05aH07,S05aH08,S01aH02,S04aH04,S03aH02,S04aH05,S04aH08,S04aH06,S05aH04,S06aH02,S06aH03,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S03aH04,S04aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05</t>
+    <t>S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S05aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S03aH03,S04aH02,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S04aH05,S04aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH09,S03aH08,S03aH10,S06aH08,S02aH02,S04aH10,S06aH10,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S01aH08,S02aH08,S04aH02,S05aH08,S06aH09,S03aH09,S05aH09,S03aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S01aH10,S03aH02,S01aH02,S05aH10</t>
+    <t>S02aH09,S04aH09,S05aH01,S04aH02,S01aH02,S05aH10,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S03aH09,S05aH09,S03aH01,S02aH02,S04aH10,S06aH10,S01aH10,S03aH02,S01aH08,S02aH08,S01aH09,S02aH01,S02aH10,S05aH02,S06aH09,S05aH08</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH09,S03aH08,S03aH10,S06aH08,S02aH02,S04aH10,S06aH10,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S01aH08,S02aH08,S04aH02,S05aH08,S06aH09,S03aH09,S05aH09,S03aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S01aH10,S03aH02,S01aH02,S05aH10</v>
+        <v>S02aH09,S04aH09,S05aH01,S04aH02,S01aH02,S05aH10,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S03aH09,S05aH09,S03aH01,S02aH02,S04aH10,S06aH10,S01aH10,S03aH02,S01aH08,S02aH08,S01aH09,S02aH01,S02aH10,S05aH02,S06aH09,S05aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S03aH03,S01aH06,S02aH03,S05aH07,S05aH08,S01aH02,S04aH04,S03aH02,S04aH05,S04aH08,S04aH06,S05aH04,S06aH02,S06aH03,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S03aH04,S04aH03,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05</v>
+        <v>S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S05aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S03aH03,S04aH02,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S04aH05,S04aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1512,7 +1512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D8DC720-769C-46E7-AD28-60B9B539523F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C91A2334-B7F9-48C6-9CC9-8C45784EE821}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1656,7 +1656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ABF0E18-CBE6-40D9-9C02-AF9633593846}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA6551F-FB65-453C-AEE5-6E02E3F7FA80}">
   <dimension ref="B9:O2170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46358,7 +46358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B5753E-50C6-47EC-A4B3-C2943FC28815}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE1534EA-AC88-4D5F-9F9E-AC41A9A64165}">
   <dimension ref="B9:IV66"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -69709,7 +69709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B1FDA3-A1A6-4C1A-94FB-3749FD6043FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B23625-3A90-4402-A47A-2E6006219160}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70579,7 +70579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05906001-6C24-441A-B6BC-7D2DBD66901B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF058BFE-7C16-4BC7-AAFF-D92D501C4B92}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71926,7 +71926,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEEBD428-E121-494D-B7F3-6195D1BDAF6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11D25EC-4503-4694-82FE-90640002C373}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -72613,7 +72613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0F8F627-2A68-4E1D-BECF-FF9AEEA3AEC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA155681-6EA2-48E6-9178-7490ABC2E946}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
